--- a/output/pdf_financials_xlsx/TMET.xlsx
+++ b/output/pdf_financials_xlsx/TMET.xlsx
@@ -3428,10 +3428,10 @@
         <v>0</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.000545</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.003871</v>
       </c>
     </row>
     <row r="104">
@@ -3512,10 +3512,10 @@
         <v>-0.10829</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.005376</v>
+        <v>-0.004831</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.003804</v>
+        <v>-6.7e-05</v>
       </c>
     </row>
     <row r="107">
@@ -4533,7 +4533,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -8280,7 +8284,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TMET.xlsx
+++ b/output/pdf_financials_xlsx/TMET.xlsx
@@ -697,10 +697,10 @@
         <v>0.293128</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.409893</v>
+        <v>0.511949</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.385762</v>
+        <v>0.489614</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         <v>-0.293128</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.409893</v>
+        <v>-0.511949</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.385762</v>
+        <v>-0.489614</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000935</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003218</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002405</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.011344</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.104135</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.07346999999999999</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -1229,22 +1229,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.010743</v>
+        <v>-0.011678</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.174479</v>
+        <v>-0.177697</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.036466</v>
+        <v>-0.038871</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.738836</v>
+        <v>-0.75018</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.105925</v>
+        <v>-0.21006</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.025824</v>
+        <v>-0.09929399999999999</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.010743</v>
+        <v>-0.011678</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.174479</v>
+        <v>-0.177697</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.036466</v>
+        <v>-0.038871</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.738836</v>
+        <v>-0.75018</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.105925</v>
+        <v>-0.21006</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.025824</v>
+        <v>-0.09929399999999999</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1440,25 +1440,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.141588</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.332922</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.256625</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.14859</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.235989</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.431105</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.202235</v>
       </c>
     </row>
     <row r="35">
@@ -1496,25 +1496,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.141588</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.332922</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.256625</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.14859</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.235989</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.431105</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.202235</v>
       </c>
     </row>
     <row r="37">
@@ -1835,22 +1835,22 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.332922</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.257258</v>
+        <v>0.000633</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.206502</v>
+        <v>0.057912</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.276102</v>
+        <v>0.040113</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.503935</v>
+        <v>0.07283000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.244362</v>
+        <v>0.042127</v>
       </c>
     </row>
     <row r="49">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -10668,13 +10668,13 @@
         </is>
       </c>
       <c r="H126" s="5" t="n">
-        <v>-0.293128</v>
+        <v>0.293128</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>-0.511949</v>
+        <v>0.511949</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>-0.489614</v>
+        <v>0.489614</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">

--- a/output/pdf_financials_xlsx/TMET.xlsx
+++ b/output/pdf_financials_xlsx/TMET.xlsx
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000669</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.012</v>
+        <v>-0.012669</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.067134</v>
+        <v>0.06631099999999999</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.04069</v>
@@ -10092,7 +10092,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>-0.000669</v>
       </c>
